--- a/data/trans_dic/IP12B$vomitos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,43</t>
+          <t>0,0; 48,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,99</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 38,02</t>
+          <t>4,26; 35,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,33</t>
+          <t>0,0; 19,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 14,71</t>
+          <t>1,83; 15,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,85</t>
+          <t>0,0; 9,73</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,9</t>
+          <t>0,0; 28,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,66</t>
+          <t>0,0; 30,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,16</t>
+          <t>0,0; 38,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,25</t>
+          <t>0,0; 24,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,43</t>
+          <t>0,0; 19,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 14,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 10,53</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,32</t>
+          <t>0,0; 25,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,76</t>
+          <t>0,0; 37,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,69</t>
+          <t>0,0; 15,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,86</t>
+          <t>0,0; 23,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,7</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,36</t>
+          <t>1,38; 12,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,25</t>
+          <t>1,36; 11,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,53</t>
+          <t>1,01; 9,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,75</t>
+          <t>2,02; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,08</t>
+          <t>1,05; 6,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,71</t>
+          <t>0,54; 5,31</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4990</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6108</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>516; 4236</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3986</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>516; 4355</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3486</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3675</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2910</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3158</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3867</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4111</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4086</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2899</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3925</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3930</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3271</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4112</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4458</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4291</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>607; 5510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4823</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3944</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>637; 5211</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>642; 6073</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3509</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1827; 8285</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7923</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>558; 5471</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$vomitos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,86</t>
+          <t>0,0; 45,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 17,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 35,02</t>
+          <t>4,22; 35,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,66</t>
+          <t>0,0; 18,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 15,42</t>
+          <t>1,82; 16,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,0; 11,29</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,95</t>
+          <t>0,0; 20,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,9</t>
+          <t>0,0; 33,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,15</t>
+          <t>0,0; 32,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,26</t>
+          <t>0,0; 23,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,6</t>
+          <t>0,0; 18,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,84</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,53</t>
+          <t>0,0; 10,91</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,24</t>
+          <t>0,0; 22,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,45</t>
+          <t>0,0; 38,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,5</t>
+          <t>0,0; 21,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,71</t>
+          <t>0,0; 23,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 12,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,56</t>
+          <t>1,45; 13,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,15</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,16</t>
+          <t>1,37; 11,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,56</t>
+          <t>1,01; 10,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,15</t>
+          <t>2,06; 9,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,35</t>
+          <t>1,03; 6,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,31</t>
+          <t>0,54; 4,67</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 4662</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6108</t>
+          <t>0; 4877</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>516; 4236</t>
+          <t>510; 4250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3986</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>516; 4355</t>
+          <t>514; 4641</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3486</t>
+          <t>0; 4045</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3675</t>
+          <t>0; 2557</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2910</t>
+          <t>0; 3174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3158</t>
+          <t>0; 2731</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 3686</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 3854</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4086</t>
+          <t>0; 3201</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 3004</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>0; 3539</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3930</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>0; 4564</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4112</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 4553</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>607; 5510</t>
+          <t>634; 5999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 5561</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637; 5211</t>
+          <t>639; 5435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>642; 6073</t>
+          <t>640; 6486</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3509</t>
+          <t>0; 3728</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1827; 8285</t>
+          <t>1864; 8578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1313; 7923</t>
+          <t>1286; 8131</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>558; 5471</t>
+          <t>559; 4812</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$vomitos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,83</t>
+          <t>0,0; 19,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,56%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 35,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,25; 38,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 16,43</t>
+          <t>1,82; 14,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,29</t>
+          <t>0,0; 9,85</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,66%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,14</t>
+          <t>0,0; 32,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,99</t>
+          <t>0,0; 20,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,37</t>
+          <t>0,0; 20,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,63</t>
+          <t>0,0; 10,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,91</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,06%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,76</t>
+          <t>0,0; 17,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,62</t>
+          <t>0,0; 25,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,73</t>
+          <t>0,0; 23,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,42</t>
+          <t>0,0; 11,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,67</t>
+          <t>1,35; 11,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>1,01; 9,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,64</t>
+          <t>1,23; 12,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,21</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,47</t>
+          <t>2,1; 9,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,51</t>
+          <t>1,03; 7,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,67</t>
+          <t>0,54; 4,71</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4662</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4877</t>
+          <t>0; 5468</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>510; 4250</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>514; 4599</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3514</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>514; 4641</t>
+          <t>515; 4155</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4045</t>
+          <t>0; 3528</t>
         </is>
       </c>
     </row>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2557</t>
+          <t>0; 2662</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3174</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2731</t>
+          <t>0; 2654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2604</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3686</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3854</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3201</t>
+          <t>0; 2787</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>0; 3054</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>787</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3539</t>
+          <t>0; 3733</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4564</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4115</t>
+          <t>0; 4137</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4553</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2313</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1414</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>634; 5999</t>
+          <t>631; 5254</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5561</t>
+          <t>644; 6058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>639; 5435</t>
+          <t>538; 5422</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>640; 6486</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3728</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1864; 8578</t>
+          <t>1904; 8831</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1286; 8131</t>
+          <t>1284; 8837</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>559; 4812</t>
+          <t>557; 4848</t>
         </is>
       </c>
     </row>
